--- a/Excel-XLSX/UN-WSH.xlsx
+++ b/Excel-XLSX/UN-WSH.xlsx
@@ -30,7 +30,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>d5vM3Y</t>
+    <t>8rygA8</t>
   </si>
   <si>
     <t>0</t>
